--- a/tame_output/ON/bt/strategyON_20240717.xlsx
+++ b/tame_output/ON/bt/strategyON_20240717.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>44.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.9%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.9%</t>
+          <t>-67.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.0%</t>
+          <t>458.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-499.7%</t>
+          <t>-500.3%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-145.6%</t>
+          <t>-145.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-136.5%</t>
+          <t>-137.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-139.3%</t>
+          <t>-147.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-34.2%</t>
         </is>
       </c>
     </row>
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.043498623601308</v>
+        <v>-2.189853714327854</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.390012326571714</v>
+        <v>2.331470290281096</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.132981408433784</v>
+        <v>1.019901412372544</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.887557045386255</v>
+        <v>3.819709047749511</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.050407329100989</v>
+        <v>-2.196762419827535</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.40032225123776</v>
+        <v>2.341780214947142</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.132981408433784</v>
+        <v>1.019901412372544</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.900630452252174</v>
+        <v>3.83278245461543</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.051968971915849</v>
+        <v>-2.198324062642395</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.399697594111816</v>
+        <v>2.341155557821198</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.132981408433784</v>
+        <v>1.019901412372544</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.900630452252174</v>
+        <v>3.83278245461543</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.079869759025322</v>
+        <v>-2.226224849751868</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.387061320395029</v>
+        <v>2.328519284104411</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.098384484290849</v>
+        <v>0.985304488229609</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.878396338893415</v>
+        <v>3.810548341256671</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.082902756537996</v>
+        <v>-2.229257847264542</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.382612565367158</v>
+        <v>2.32407052907654</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.095351486778175</v>
+        <v>0.9822714907169352</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.873340984363009</v>
+        <v>3.805492986726265</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.102964077814502</v>
+        <v>-2.249319168541049</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.441293996447059</v>
+        <v>2.382751960156441</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.075290165501668</v>
+        <v>0.9622101694404281</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.928010151187609</v>
+        <v>3.860162153550865</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.359684895809326</v>
+        <v>-2.506039986535872</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.478917388250977</v>
+        <v>2.420375351960359</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.9668755913578532</v>
+        <v>0.8537955952966133</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.003273125703167</v>
+        <v>3.935425128066423</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.513671313585467</v>
+        <v>-2.660026404312013</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.48630309028616</v>
+        <v>2.427761053995542</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.9668755913578532</v>
+        <v>0.8537955952966133</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.072253394848807</v>
+        <v>4.004405397212063</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.463149409757801</v>
+        <v>-2.609504500484347</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.492563053937348</v>
+        <v>2.434021017646729</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.9668755913578532</v>
+        <v>0.8537955952966133</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.058304596968927</v>
+        <v>3.990456599332184</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.715624563765526</v>
+        <v>-2.861979654492072</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.403443481389671</v>
+        <v>2.344901445099053</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.9668755913578532</v>
+        <v>0.8537955952966133</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.070175086024341</v>
+        <v>4.002327088387597</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.985097365687234</v>
+        <v>-3.13145245641378</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.296864895139932</v>
+        <v>2.238322858849314</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.9668755913578532</v>
+        <v>0.8537955952966133</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.071385620543285</v>
+        <v>4.003537622906541</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.142641437416675</v>
+        <v>-3.288996528143221</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.237969008675477</v>
+        <v>2.179426972384859</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.8999737862175787</v>
+        <v>0.7868937901563389</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.035366279686442</v>
+        <v>3.967518282049697</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.271491988118722</v>
+        <v>-3.417847078845268</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.181506641130848</v>
+        <v>2.12296460484023</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.8589803773668572</v>
+        <v>0.7459003813056173</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.005848087112199</v>
+        <v>3.938000089475454</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.388459680757613</v>
+        <v>-3.534814771484159</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.296923620774336</v>
+        <v>2.238381584483717</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.8589803773668572</v>
+        <v>0.7459003813056173</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.168052143811242</v>
+        <v>4.100204146174499</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.473177622978566</v>
+        <v>-3.619532713705112</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.257883081849768</v>
+        <v>2.19934104555915</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.7738643484388108</v>
+        <v>0.6607843523775709</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.111829164418229</v>
+        <v>4.043981166781485</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.55511244124745</v>
+        <v>-3.701467531973996</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.235338572110706</v>
+        <v>2.176796535820087</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.7639296028517306</v>
+        <v>0.6508496067904908</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.116097734634472</v>
+        <v>4.048249736997728</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.501374267847188</v>
+        <v>-3.647729358573734</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.265759479926714</v>
+        <v>2.207217443636095</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.8176677762519927</v>
+        <v>0.7045877801907529</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.157266277130532</v>
+        <v>4.089418279493787</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.716864678902795</v>
+        <v>3.725495127255543</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.381610314876014</v>
+        <v>-3.38770789368607</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.305817948359358</v>
+        <v>2.303378916835336</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.8468392067286672</v>
+        <v>0.7657663409344515</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.166922022660712</v>
+        <v>4.118278303184182</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240717.xlsx
+++ b/tame_output/ON/bt/strategyON_20240717.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.0%</t>
+          <t>-67.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.6%</t>
+          <t>458.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-500.3%</t>
+          <t>-515.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-145.9%</t>
+          <t>-151.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-147.4%</t>
+          <t>-151.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-36.5%</t>
         </is>
       </c>
     </row>
@@ -48172,16 +48172,16 @@
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.38770789368607</v>
+        <v>-3.537723075096512</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.303378916835336</v>
+        <v>2.243372844271159</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7657663409344515</v>
+        <v>0.7277923521080281</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.118278303184182</v>
+        <v>4.095493909888329</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240717.xlsx
+++ b/tame_output/ON/bt/strategyON_20240717.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>44.3%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>122.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-90.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2027"/>
+  <dimension ref="A1:G2028"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.725495127255543</v>
+        <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
@@ -48182,6 +48182,29 @@
       </c>
       <c r="G2027" t="n">
         <v>4.095493909888329</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" s="2" t="n">
+        <v>45490</v>
+      </c>
+      <c r="B2028" t="n">
+        <v>3.726547461015467</v>
+      </c>
+      <c r="C2028" t="n">
+        <v>3.559391205133759</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>-3.537723075096512</v>
+      </c>
+      <c r="E2028" t="n">
+        <v>2.243372844271159</v>
+      </c>
+      <c r="F2028" t="n">
+        <v>0.7277923521080281</v>
+      </c>
+      <c r="G2028" t="n">
+        <v>3.552455002120127</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240717.xlsx
+++ b/tame_output/ON/bt/strategyON_20240717.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>47.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-73.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.1%</t>
+          <t>122.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.9%</t>
+          <t>-68.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-515.3%</t>
+          <t>-518.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-151.9%</t>
+          <t>-152.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-137.4%</t>
+          <t>-134.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-151.2%</t>
+          <t>-138.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-90.8%</t>
+          <t>-28.1%</t>
         </is>
       </c>
     </row>
@@ -47804,10 +47804,10 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.196762419827535</v>
+        <v>-2.358116249616525</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.341780214947142</v>
+        <v>2.277238683031546</v>
       </c>
       <c r="F2011" t="n">
         <v>1.019901412372544</v>
@@ -47827,10 +47827,10 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.198324062642395</v>
+        <v>-2.359677892431385</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.341155557821198</v>
+        <v>2.276614025905602</v>
       </c>
       <c r="F2012" t="n">
         <v>1.019901412372544</v>
@@ -47850,10 +47850,10 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.226224849751868</v>
+        <v>-2.387578679540858</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.328519284104411</v>
+        <v>2.263977752188814</v>
       </c>
       <c r="F2013" t="n">
         <v>0.985304488229609</v>
@@ -47873,10 +47873,10 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.229257847264542</v>
+        <v>-2.390611677053532</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.32407052907654</v>
+        <v>2.259528997160944</v>
       </c>
       <c r="F2014" t="n">
         <v>0.9822714907169352</v>
@@ -47896,10 +47896,10 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.249319168541049</v>
+        <v>-2.410672998330039</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.382751960156441</v>
+        <v>2.318210428240845</v>
       </c>
       <c r="F2015" t="n">
         <v>0.9622101694404281</v>
@@ -47919,10 +47919,10 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.506039986535872</v>
+        <v>-2.667393816324863</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.420375351960359</v>
+        <v>2.355833820044762</v>
       </c>
       <c r="F2016" t="n">
         <v>0.8537955952966133</v>
@@ -47942,10 +47942,10 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.660026404312013</v>
+        <v>-2.821380234101003</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.427761053995542</v>
+        <v>2.363219522079945</v>
       </c>
       <c r="F2017" t="n">
         <v>0.8537955952966133</v>
@@ -47965,10 +47965,10 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.609504500484347</v>
+        <v>-2.770858330273338</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.434021017646729</v>
+        <v>2.369479485731133</v>
       </c>
       <c r="F2018" t="n">
         <v>0.8537955952966133</v>
@@ -47988,10 +47988,10 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.861979654492072</v>
+        <v>-3.023333484281062</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.344901445099053</v>
+        <v>2.280359913183457</v>
       </c>
       <c r="F2019" t="n">
         <v>0.8537955952966133</v>
@@ -48011,10 +48011,10 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.13145245641378</v>
+        <v>-3.29280628620277</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.238322858849314</v>
+        <v>2.173781326933717</v>
       </c>
       <c r="F2020" t="n">
         <v>0.8537955952966133</v>
@@ -48034,10 +48034,10 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.288996528143221</v>
+        <v>-3.450350357932212</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.179426972384859</v>
+        <v>2.114885440469263</v>
       </c>
       <c r="F2021" t="n">
         <v>0.7868937901563389</v>
@@ -48057,10 +48057,10 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.417847078845268</v>
+        <v>-3.579200908634258</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.12296460484023</v>
+        <v>2.058423072924633</v>
       </c>
       <c r="F2022" t="n">
         <v>0.7459003813056173</v>
@@ -48080,10 +48080,10 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.534814771484159</v>
+        <v>-3.696168601273149</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.238381584483717</v>
+        <v>2.173840052568121</v>
       </c>
       <c r="F2023" t="n">
         <v>0.7459003813056173</v>
@@ -48103,10 +48103,10 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.619532713705112</v>
+        <v>-3.780886543494103</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.19934104555915</v>
+        <v>2.134799513643554</v>
       </c>
       <c r="F2024" t="n">
         <v>0.6607843523775709</v>
@@ -48126,10 +48126,10 @@
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.701467531973996</v>
+        <v>-3.862821361762987</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.176796535820087</v>
+        <v>2.112255003904491</v>
       </c>
       <c r="F2025" t="n">
         <v>0.6508496067904908</v>
@@ -48149,10 +48149,10 @@
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.647729358573734</v>
+        <v>-3.809083188362724</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.207217443636095</v>
+        <v>2.142675911720499</v>
       </c>
       <c r="F2026" t="n">
         <v>0.7045877801907529</v>
@@ -48172,10 +48172,10 @@
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.537723075096512</v>
+        <v>-3.699076904885502</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.243372844271159</v>
+        <v>2.178831312355563</v>
       </c>
       <c r="F2027" t="n">
         <v>0.7277923521080281</v>
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.726547461015467</v>
+        <v>3.753720747048118</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.559391205133759</v>
+        <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.537723075096512</v>
+        <v>-3.566662745538538</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.243372844271159</v>
+        <v>2.236046986816323</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7277923521080281</v>
+        <v>0.8602065114549928</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.552455002120127</v>
+        <v>4.179192416218481</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240717.xlsx
+++ b/tame_output/ON/bt/strategyON_20240717.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.0%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.6%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.1%</t>
+          <t>-66.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.2%</t>
+          <t>458.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-518.2%</t>
+          <t>-500.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.6%</t>
+          <t>-145.4%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-134.9%</t>
+          <t>-135.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-138.0%</t>
+          <t>-138.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-28.5%</t>
         </is>
       </c>
     </row>
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.189853714327854</v>
+        <v>-2.043498623601308</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.331470290281096</v>
+        <v>2.390012326571714</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.019901412372544</v>
+        <v>1.132981408433784</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.819709047749511</v>
+        <v>3.887557045386255</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647104</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.358116249616525</v>
+        <v>-2.175799915698862</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.277238683031546</v>
+        <v>2.350165216598611</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.019901412372544</v>
+        <v>1.132981408433784</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.83278245461543</v>
+        <v>3.900630452252174</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.359677892431385</v>
+        <v>-2.177361558513722</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.276614025905602</v>
+        <v>2.349540559472667</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.019901412372544</v>
+        <v>1.132981408433784</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.83278245461543</v>
+        <v>3.900630452252174</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.387578679540858</v>
+        <v>-2.205262345623195</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.263977752188814</v>
+        <v>2.33690428575588</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.985304488229609</v>
+        <v>1.098384484290849</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.810548341256671</v>
+        <v>3.878396338893415</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.390611677053532</v>
+        <v>-2.208295343135869</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.259528997160944</v>
+        <v>2.332455530728009</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9822714907169352</v>
+        <v>1.095351486778175</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.805492986726265</v>
+        <v>3.873340984363009</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.410672998330039</v>
+        <v>-2.228356664412376</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.318210428240845</v>
+        <v>2.39113696180791</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9622101694404281</v>
+        <v>1.075290165501668</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.860162153550865</v>
+        <v>3.928010151187609</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.667393816324863</v>
+        <v>-2.4850774824072</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.355833820044762</v>
+        <v>2.428760353611827</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8537955952966133</v>
+        <v>0.9668755913578532</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.935425128066423</v>
+        <v>4.003273125703167</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.821380234101003</v>
+        <v>-2.63906390018334</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.363219522079945</v>
+        <v>2.436146055647011</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8537955952966133</v>
+        <v>0.9668755913578532</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.004405397212063</v>
+        <v>4.072253394848807</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.770858330273338</v>
+        <v>-2.588541996355674</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.369479485731133</v>
+        <v>2.442406019298199</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8537955952966133</v>
+        <v>0.9668755913578532</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.990456599332184</v>
+        <v>4.058304596968927</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.023333484281062</v>
+        <v>-2.841017150363399</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.280359913183457</v>
+        <v>2.353286446750523</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8537955952966133</v>
+        <v>0.9668755913578532</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.002327088387597</v>
+        <v>4.070175086024341</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.29280628620277</v>
+        <v>-3.110489952285107</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.173781326933717</v>
+        <v>2.246707860500783</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8537955952966133</v>
+        <v>0.9668755913578532</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.003537622906541</v>
+        <v>4.071385620543285</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.450350357932212</v>
+        <v>-3.268034024014548</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.114885440469263</v>
+        <v>2.187811974036328</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7868937901563389</v>
+        <v>0.8999737862175787</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.967518282049697</v>
+        <v>4.035366279686442</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.579200908634258</v>
+        <v>-3.396884574716595</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.058423072924633</v>
+        <v>2.131349606491699</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7459003813056173</v>
+        <v>0.8589803773668572</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.938000089475454</v>
+        <v>4.005848087112199</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.696168601273149</v>
+        <v>-3.513852267355486</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.173840052568121</v>
+        <v>2.246766586135187</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7459003813056173</v>
+        <v>0.8589803773668572</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.100204146174499</v>
+        <v>4.168052143811242</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.780886543494103</v>
+        <v>-3.598570209576439</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.134799513643554</v>
+        <v>2.207726047210619</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6607843523775709</v>
+        <v>0.7738643484388108</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.043981166781485</v>
+        <v>4.111829164418229</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.862821361762987</v>
+        <v>-3.680505027845323</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.112255003904491</v>
+        <v>2.185181537471557</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6508496067904908</v>
+        <v>0.7639296028517306</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.048249736997728</v>
+        <v>4.116097734634472</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.809083188362724</v>
+        <v>-3.626766854445061</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.142675911720499</v>
+        <v>2.215602445287564</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.7045877801907529</v>
+        <v>0.8176677762519927</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.089418279493787</v>
+        <v>4.157266277130532</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798310944616946</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.699076904885502</v>
+        <v>-3.516760570967839</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.178831312355563</v>
+        <v>2.251757845922628</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7277923521080281</v>
+        <v>0.8408723481692679</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.095493909888329</v>
+        <v>4.163341907525072</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.753720747048118</v>
+        <v>3.753720747048117</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.566662745538538</v>
+        <v>-3.385757877982468</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.236046986816323</v>
+        <v>2.308408933838751</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.8602065114549928</v>
+        <v>0.853278216458725</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.179192416218481</v>
+        <v>4.175035439220721</v>
       </c>
     </row>
   </sheetData>
